--- a/docs/descargas/fallecidos_inec_2019.xlsx
+++ b/docs/descargas/fallecidos_inec_2019.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="Re324710332504ec1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="R9162a428265a4af6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2020" sheetId="3" r:id="R5811051ed39549da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="4" r:id="R4c0d91e91a3a42cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2022" sheetId="5" r:id="Rea1df5b3c4834915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2023" sheetId="6" r:id="R81f33df6cdfd4d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="7" r:id="R414b9fe07f8f482f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Léeme" sheetId="1" r:id="R281e78a60a9b4d8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología" sheetId="2" r:id="Rb4d78a3cb6674265"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2020" sheetId="3" r:id="R5a479e4d75b74c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2021" sheetId="4" r:id="R79664e951cab4672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2022" sheetId="5" r:id="R938e622df6d54389"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2023" sheetId="6" r:id="R0b564df609884d15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Año 2024" sheetId="7" r:id="Rb5a0687643764468"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -550,7 +550,7 @@
         <x:v>Producto</x:v>
       </x:c>
       <x:c r="B4" s="7" t="str">
-        <x:v>Descarga pública del Catálogo de datos del Observatorio REDSA</x:v>
+        <x:v>Descarga pública del Catálogo de datos del Observatorio de Seguridad Vial y Movilidad Sostenible</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
